--- a/data/estad_portales/Rendimiento_período-p3.xlsx
+++ b/data/estad_portales/Rendimiento_período-p3.xlsx
@@ -427,25 +427,25 @@
     </row>
     <row r="2" ht="17" customHeight="1">
       <c r="A2" s="2" t="str">
-        <v>04/09/2026</v>
+        <v>11/09/2026</v>
       </c>
       <c r="B2" s="2">
-        <v>4601</v>
+        <v>4291</v>
       </c>
       <c r="C2" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D2" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2">
         <v>0</v>
       </c>
       <c r="F2" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G2" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H2" s="2" t="str">
         <v/>
@@ -453,22 +453,22 @@
     </row>
     <row r="3" ht="17" customHeight="1">
       <c r="A3" s="2" t="str">
-        <v>05/09/2026</v>
+        <v>12/09/2026</v>
       </c>
       <c r="B3" s="2">
-        <v>4181</v>
+        <v>3846</v>
       </c>
       <c r="C3" s="2">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="D3" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E3" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
@@ -479,22 +479,22 @@
     </row>
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="2" t="str">
-        <v>06/09/2026</v>
+        <v>13/09/2026</v>
       </c>
       <c r="B4" s="2">
-        <v>5054</v>
+        <v>4633</v>
       </c>
       <c r="C4" s="2">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="D4" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="2">
         <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G4" s="2">
         <v>1</v>
@@ -505,25 +505,25 @@
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="2" t="str">
-        <v>07/09/2026</v>
+        <v>14/09/2026</v>
       </c>
       <c r="B5" s="2">
-        <v>5887</v>
+        <v>5645</v>
       </c>
       <c r="C5" s="2">
-        <v>404</v>
+        <v>441</v>
       </c>
       <c r="D5" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E5" s="2">
         <v>4</v>
       </c>
       <c r="F5" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G5" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H5" s="2" t="str">
         <v/>
@@ -531,25 +531,25 @@
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="2" t="str">
-        <v>08/09/2026</v>
+        <v>15/09/2026</v>
       </c>
       <c r="B6" s="2">
-        <v>5650</v>
+        <v>4063</v>
       </c>
       <c r="C6" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D6" s="2">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E6" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G6" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H6" s="2" t="str">
         <v/>
@@ -557,22 +557,22 @@
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="2" t="str">
-        <v>09/09/2026</v>
+        <v>16/09/2026</v>
       </c>
       <c r="B7" s="2">
-        <v>5106</v>
+        <v>4878</v>
       </c>
       <c r="C7" s="2">
-        <v>256</v>
+        <v>323</v>
       </c>
       <c r="D7" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E7" s="2">
         <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -583,25 +583,25 @@
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="2" t="str">
-        <v>10/09/2026</v>
+        <v>17/09/2026</v>
       </c>
       <c r="B8" s="2">
-        <v>4667</v>
+        <v>5806</v>
       </c>
       <c r="C8" s="2">
-        <v>274</v>
+        <v>451</v>
       </c>
       <c r="D8" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E8" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G8" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H8" s="2" t="str">
         <v/>
